--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:45</t>
+    <t xml:space="preserve">2026-09-24 01:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -579,10 +579,10 @@
         <v>-0.85</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="3">
@@ -602,10 +602,10 @@
         <v>-0.72</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="4">
@@ -625,10 +625,10 @@
         <v>-0.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="5">
@@ -648,10 +648,10 @@
         <v>0.85</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="6">
@@ -671,10 +671,10 @@
         <v>0.21</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
@@ -715,7 +715,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -755,7 +755,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.21</v>
@@ -847,10 +847,10 @@
         <v>0.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="15">
@@ -870,10 +870,10 @@
         <v>0.27</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="16">
@@ -962,10 +962,10 @@
         <v>-0.79</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="20">
@@ -985,7 +985,7 @@
         <v>-0.83</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.5</v>
@@ -1005,13 +1005,13 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.07</v>
+        <v>0.2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="22">
@@ -1028,13 +1028,13 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="23">
@@ -1051,13 +1051,13 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.57</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -1077,10 +1077,10 @@
         <v>-0.4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="25">
@@ -1100,10 +1100,10 @@
         <v>-0.59</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="26">
@@ -1123,10 +1123,10 @@
         <v>-0.41</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="27">
@@ -1146,10 +1146,10 @@
         <v>0.59</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -1169,10 +1169,10 @@
         <v>-0.15</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="29">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="G30" s="2"/>
     </row>
@@ -1299,7 +1299,7 @@
         <v>0.48</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0.3</v>
@@ -1345,10 +1345,10 @@
         <v>0.57</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="37">
@@ -1368,10 +1368,10 @@
         <v>0.12</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="38">
@@ -1440,7 +1440,7 @@
         <v>-0.64</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="41">
@@ -1503,13 +1503,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="44">
@@ -1529,10 +1529,10 @@
         <v>0.32</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="45">
@@ -1549,13 +1549,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.58</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.17</v>
+        <v>-0.69</v>
       </c>
     </row>
     <row r="46">
@@ -2001,13 +2001,13 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.12</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="66">
@@ -2027,10 +2027,10 @@
         <v>-0.36</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="67">
@@ -2047,13 +2047,13 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>-0.23</v>
+        <v>0.74</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:34</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
